--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N12_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N12_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.55240852946685</v>
+        <v>5.939766386038364</v>
       </c>
       <c r="D2" t="n">
-        <v>35.503004802112</v>
+        <v>5.769238280343201</v>
       </c>
       <c r="E2" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F2" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.39811338070298</v>
+        <v>6.402193424364235</v>
       </c>
       <c r="D3" t="n">
-        <v>13.76754084956491</v>
+        <v>2.237225388054299</v>
       </c>
       <c r="E3" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F3" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.15715434985096</v>
+        <v>4.250537581850781</v>
       </c>
       <c r="D4" t="n">
-        <v>25.71298128432649</v>
+        <v>4.178359458703054</v>
       </c>
       <c r="E4" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F4" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.20780395318862</v>
+        <v>3.771268142393152</v>
       </c>
       <c r="D5" t="n">
-        <v>18.58617003322751</v>
+        <v>3.02025263039947</v>
       </c>
       <c r="E5" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F5" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.22198144925346</v>
+        <v>6.861071985503687</v>
       </c>
       <c r="D6" t="n">
-        <v>41.14476471090739</v>
+        <v>6.686024265522451</v>
       </c>
       <c r="E6" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F6" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.69939490374876</v>
+        <v>3.363651671859173</v>
       </c>
       <c r="D7" t="n">
-        <v>22.02230424809273</v>
+        <v>3.578624440315069</v>
       </c>
       <c r="E7" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F7" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>5.474363710867447</v>
+        <v>0.8895841030159601</v>
       </c>
       <c r="D8" t="n">
-        <v>9.240997612784437</v>
+        <v>1.501662112077471</v>
       </c>
       <c r="E8" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F8" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.42891506705853</v>
+        <v>3.482198698397011</v>
       </c>
       <c r="D9" t="n">
-        <v>20.79636158331012</v>
+        <v>3.379408757287894</v>
       </c>
       <c r="E9" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F9" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.25986965591783</v>
+        <v>7.029728819086647</v>
       </c>
       <c r="D10" t="n">
-        <v>42.57908927329115</v>
+        <v>6.919102006909811</v>
       </c>
       <c r="E10" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F10" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.811616400702452</v>
+        <v>1.106887665114148</v>
       </c>
       <c r="D11" t="n">
-        <v>2.621552925668898</v>
+        <v>0.426002350421196</v>
       </c>
       <c r="E11" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F11" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>22.4356048793141</v>
+        <v>3.645785792888542</v>
       </c>
       <c r="D12" t="n">
-        <v>21.80840365274236</v>
+        <v>3.543865593570634</v>
       </c>
       <c r="E12" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F12" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.69980028129324</v>
+        <v>6.938717545710152</v>
       </c>
       <c r="D13" t="n">
-        <v>43.45157066617897</v>
+        <v>7.060880233254082</v>
       </c>
       <c r="E13" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F13" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.62239231195422</v>
+        <v>1.401138750692561</v>
       </c>
       <c r="D14" t="n">
-        <v>9.469537301263921</v>
+        <v>1.538799811455387</v>
       </c>
       <c r="E14" t="n">
-        <v>13.27729076190378</v>
+        <v>2.157559748809364</v>
       </c>
       <c r="F14" t="n">
-        <v>12.97801752560236</v>
+        <v>2.108927847910383</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
